--- a/artfynd/A 1019-2026 artfynd.xlsx
+++ b/artfynd/A 1019-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111721864</v>
+        <v>111722457</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516210</v>
+        <v>516166</v>
       </c>
       <c r="R2" t="n">
-        <v>6698257</v>
+        <v>6698232</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -771,69 +755,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Niklas Rehn, Lars-Erik Nilsson, Malte Lindberg, Anna-Lena Thommson, Cecilia Rastad</t>
+          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111722181</v>
+        <v>111722556</v>
       </c>
       <c r="B3" t="n">
-        <v>95534</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516210</v>
+        <v>516160</v>
       </c>
       <c r="R3" t="n">
-        <v>6698257</v>
+        <v>6698248</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -874,34 +853,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Niklas Rehn, Lars-Erik Nilsson, Malte Lindberg, Anna-Lena Thommson, Cecilia Rastad</t>
+          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111722457</v>
+        <v>111722030</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,35 +882,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516166</v>
+        <v>516213</v>
       </c>
       <c r="R4" t="n">
-        <v>6698232</v>
+        <v>6698267</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -996,54 +969,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111722030</v>
+        <v>111721999</v>
       </c>
       <c r="B5" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvbergsmyran, Stora Tuna , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516213</v>
+        <v>516208</v>
       </c>
       <c r="R5" t="n">
-        <v>6698267</v>
+        <v>6698278</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,83 +1042,97 @@
           <t>2023-08-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-27</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Niklas Rehn, Anna-Lena Thommson, Malte Lindberg, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111722556</v>
+        <v>111722343</v>
       </c>
       <c r="B6" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516160</v>
+        <v>516172</v>
       </c>
       <c r="R6" t="n">
-        <v>6698248</v>
+        <v>6698341</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,44 +1159,50 @@
           <t>2023-08-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-27</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Niklas Rehn, Anna-Lena Thommson, Malte Lindberg, Holger Martinussen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111722607</v>
+        <v>111721825</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,14 +1231,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516165</v>
+        <v>516208</v>
       </c>
       <c r="R7" t="n">
-        <v>6698245</v>
+        <v>6698244</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1305,15 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111721825</v>
+        <v>111721864</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,18 +1325,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ulvberget (Ulvberget), Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516208</v>
+        <v>516210</v>
       </c>
       <c r="R8" t="n">
-        <v>6698243</v>
+        <v>6698257</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1390,76 +1388,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Holger Martinussen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
+          <t>Holger Martinussen, Niklas Rehn, Lars-Erik Nilsson, Malte Lindberg, Anna-Lena Thommson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111721999</v>
+        <v>111722607</v>
       </c>
       <c r="B9" t="n">
-        <v>5164</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ulvbergsmyran, Stora Tuna , Dlr</t>
+          <t>Ulvberget, Ulvberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516209</v>
+        <v>516165</v>
       </c>
       <c r="R9" t="n">
-        <v>6698277</v>
+        <v>6698244</v>
       </c>
       <c r="S9" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,43 +1476,130 @@
           <t>2023-08-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Niklas Rehn, Anna-Lena Thommson, Malte Lindberg, Holger Martinussen</t>
+          <t>Niklas Rehn, Cecilia Rastad, Lars-Erik Nilsson, Anna-Lena Thommson, Holger Martinussen, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111722181</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ulvberget, Ulvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516210</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6698257</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Holger Martinussen, Niklas Rehn, Lars-Erik Nilsson, Malte Lindberg, Anna-Lena Thommson, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1019-2026 artfynd.xlsx
+++ b/artfynd/A 1019-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722457</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722556</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722030</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111721999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722343</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111721825</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111721864</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722607</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,8 +1645,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111722181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>